--- a/購入物品.xlsx
+++ b/購入物品.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stkyotouac-my.sharepoint.com/personal/michikawa_ryohei_6w_ms_c_kyoto-u_ac_jp/Documents/lab/7_研究室業務/2025_研究室業務/メカトロ講習/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stkyotouac-my.sharepoint.com/personal/michikawa_ryohei_6w_ms_c_kyoto-u_ac_jp/Documents/lab/7_研究室業務/2026_研究室業務/メカトロ講習/MechatronicsTraining/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="173" documentId="11_AD4D066CA252ABDACC104895E955C54673EEDF52" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB84C84D-1FE6-42AF-A691-8BEEEFACF6FC}"/>
   <bookViews>
-    <workbookView xWindow="33240" yWindow="326" windowWidth="16457" windowHeight="9497" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18120" yWindow="-7320" windowWidth="18240" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -682,17 +682,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.875" style="2" customWidth="1"/>
     <col min="3" max="3" width="23.5" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="53" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.33203125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.58203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="14.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.625" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.6640625" style="1"/>
+    <col min="9" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
